--- a/data/trans_orig/P56$nadie-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P56$nadie-Edad-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4714</t>
+          <t>5023</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5650</t>
+          <t>5614</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>900</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7883</t>
+          <t>8290</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>23,73%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2559</t>
+          <t>2216</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9408</t>
+          <t>9379</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4334</t>
+          <t>4105</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13275</t>
+          <t>12521</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9110</t>
+          <t>9064</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20205</t>
+          <t>20086</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>57,5%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>953</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6798</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>899</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7488</t>
+          <t>7417</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2643</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11203</t>
+          <t>11673</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>33,41%</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>5198</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>1903</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9619</t>
+          <t>9695</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2838</t>
+          <t>2781</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12230</t>
+          <t>12127</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>34,71%</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4695</t>
+          <t>4199</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3832</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,7%</t>
         </is>
       </c>
     </row>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3632</t>
+          <t>4358</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>882</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7107</t>
+          <t>6938</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1044</t>
+          <t>927</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8815</t>
+          <t>8073</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1383,12 +1383,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>23,11%</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4624</t>
+          <t>4742</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3981</t>
+          <t>4314</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5512</t>
+          <t>5416</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3543</t>
+          <t>3594</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15321</t>
+          <t>14361</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>4859</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17414</t>
+          <t>17867</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,72%</t>
         </is>
       </c>
     </row>
@@ -1980,12 +1980,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9214</t>
+          <t>8817</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>20391</t>
+          <t>20101</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1995,12 +1995,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>56,76%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9515</t>
+          <t>8693</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2050,12 +2050,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>9632</t>
+          <t>10845</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>24876</t>
+          <t>24439</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2065,12 +2065,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>22,86%</t>
         </is>
       </c>
     </row>
@@ -2093,12 +2093,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2684</t>
+          <t>2771</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11128</t>
+          <t>11851</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2108,12 +2108,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,12 +2128,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27243</t>
+          <t>26533</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45684</t>
+          <t>44078</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2143,12 +2143,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31898</t>
+          <t>30785</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53133</t>
+          <t>52414</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2178,12 +2178,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>49,04%</t>
         </is>
       </c>
     </row>
@@ -2206,12 +2206,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4302</t>
+          <t>3659</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13079</t>
+          <t>13588</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2221,12 +2221,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,12 +2241,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5917</t>
+          <t>5979</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19463</t>
+          <t>19620</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2256,12 +2256,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,12 +2276,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13068</t>
+          <t>13266</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>28849</t>
+          <t>29712</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2291,12 +2291,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,8%</t>
         </is>
       </c>
     </row>
@@ -2319,12 +2319,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8076</t>
+          <t>8116</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2334,12 +2334,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5614</t>
+          <t>5605</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10173</t>
+          <t>9437</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6832</t>
+          <t>6292</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,12 +2467,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3297</t>
+          <t>3413</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14866</t>
+          <t>15320</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,12 +2502,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5727</t>
+          <t>5155</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17921</t>
+          <t>17730</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,59%</t>
         </is>
       </c>
     </row>
@@ -2580,12 +2580,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2188</t>
+          <t>2182</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11653</t>
+          <t>11993</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,12 +2615,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2216</t>
+          <t>2119</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12438</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>10,66%</t>
         </is>
       </c>
     </row>
@@ -3001,12 +3001,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>930</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7709</t>
+          <t>7811</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3016,12 +3016,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4787</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>18084</t>
+          <t>17262</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3051,12 +3051,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7792</t>
+          <t>7687</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>21243</t>
+          <t>21536</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3086,12 +3086,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,18%</t>
         </is>
       </c>
     </row>
@@ -3114,12 +3114,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14530</t>
+          <t>13462</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>27529</t>
+          <t>26214</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3129,12 +3129,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5442</t>
+          <t>5841</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>17941</t>
+          <t>19438</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3164,12 +3164,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>22241</t>
+          <t>22875</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>41080</t>
+          <t>42002</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3199,12 +3199,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,62%</t>
         </is>
       </c>
     </row>
@@ -3227,12 +3227,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4817</t>
+          <t>4577</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>15129</t>
+          <t>15035</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3242,12 +3242,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>28525</t>
+          <t>28318</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>48161</t>
+          <t>48416</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3277,12 +3277,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>37688</t>
+          <t>37203</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>59486</t>
+          <t>58298</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3312,12 +3312,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>41,11%</t>
         </is>
       </c>
     </row>
@@ -3340,12 +3340,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>4961</t>
+          <t>5663</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>16299</t>
+          <t>16148</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3355,12 +3355,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,12 +3375,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>10165</t>
+          <t>9655</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>26329</t>
+          <t>25607</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3390,12 +3390,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,12 +3410,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>17788</t>
+          <t>18120</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>37377</t>
+          <t>37429</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3425,12 +3425,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,39%</t>
         </is>
       </c>
     </row>
@@ -3453,12 +3453,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7266</t>
+          <t>7720</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6632</t>
+          <t>6763</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,12 +3523,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1978</t>
+          <t>1937</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>11567</t>
+          <t>11320</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,98%</t>
         </is>
       </c>
     </row>
@@ -3566,12 +3566,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>887</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7968</t>
+          <t>7995</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3581,12 +3581,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,12 +3601,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>5267</t>
+          <t>5244</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>18327</t>
+          <t>19030</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,12 +3636,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>8667</t>
+          <t>7866</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>23499</t>
+          <t>23003</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,22%</t>
         </is>
       </c>
     </row>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2188</t>
+          <t>2251</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>12254</t>
+          <t>12977</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,12 +3749,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2331</t>
+          <t>2297</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>14510</t>
+          <t>13806</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -4370,7 +4370,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4168</t>
+          <t>4326</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3722</t>
+          <t>3767</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13754</t>
+          <t>13142</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4589</t>
+          <t>4522</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15304</t>
+          <t>15043</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4450,12 +4450,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,67%</t>
         </is>
       </c>
     </row>
@@ -4478,12 +4478,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9688</t>
+          <t>9571</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18325</t>
+          <t>18335</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4493,12 +4493,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5751</t>
+          <t>5855</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17827</t>
+          <t>17829</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4528,7 +4528,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4548,12 +4548,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18102</t>
+          <t>18058</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35017</t>
+          <t>33621</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>52,89%</t>
         </is>
       </c>
     </row>
@@ -4591,12 +4591,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8379</t>
+          <t>8615</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4606,12 +4606,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4759</t>
+          <t>4612</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16134</t>
+          <t>16007</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7425</t>
+          <t>7646</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20817</t>
+          <t>21168</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>33,3%</t>
         </is>
       </c>
     </row>
@@ -4704,12 +4704,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>926</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7917</t>
+          <t>7486</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4719,12 +4719,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4739,12 +4739,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4797</t>
+          <t>4869</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15543</t>
+          <t>15546</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7746</t>
+          <t>7295</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20317</t>
+          <t>20732</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>32,62%</t>
         </is>
       </c>
     </row>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5083</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5092</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,8%</t>
         </is>
       </c>
     </row>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5851</t>
+          <t>4658</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4965,12 +4965,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>983</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8746</t>
+          <t>9063</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4980,12 +4980,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5000,12 +5000,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1942</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>10247</t>
+          <t>10328</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5015,12 +5015,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,25%</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5851</t>
+          <t>4658</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7083</t>
+          <t>7802</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5113,12 +5113,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>975</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9111</t>
+          <t>9550</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5128,12 +5128,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>15,02%</t>
         </is>
       </c>
     </row>
@@ -5387,7 +5387,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5598</t>
+          <t>5090</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5457,7 +5457,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4372</t>
+          <t>4095</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4724</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5519,7 +5519,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5534,12 +5534,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2223</t>
+          <t>2298</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11721</t>
+          <t>13696</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5549,12 +5549,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5569,12 +5569,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>3217</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13985</t>
+          <t>13756</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5584,12 +5584,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -5612,12 +5612,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12148</t>
+          <t>12014</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>28666</t>
+          <t>28023</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5647,12 +5647,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11842</t>
+          <t>12037</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>28364</t>
+          <t>28575</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5662,12 +5662,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5682,12 +5682,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>27384</t>
+          <t>26991</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>52254</t>
+          <t>51628</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5697,12 +5697,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,45%</t>
         </is>
       </c>
     </row>
@@ -5725,12 +5725,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5784</t>
+          <t>5671</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20513</t>
+          <t>20077</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5760,12 +5760,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36757</t>
+          <t>36582</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>60839</t>
+          <t>61965</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5795,12 +5795,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>46553</t>
+          <t>45613</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>74947</t>
+          <t>73858</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>33,54%</t>
         </is>
       </c>
     </row>
@@ -5838,12 +5838,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10670</t>
+          <t>10785</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25347</t>
+          <t>25036</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5873,12 +5873,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>40749</t>
+          <t>39204</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>64019</t>
+          <t>63610</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5908,12 +5908,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>54916</t>
+          <t>55636</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>83823</t>
+          <t>83043</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>37,71%</t>
         </is>
       </c>
     </row>
@@ -5986,12 +5986,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11215</t>
+          <t>10111</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6021,12 +6021,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1119</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10919</t>
+          <t>11258</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -6064,12 +6064,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2110</t>
+          <t>2920</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12185</t>
+          <t>12837</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6079,12 +6079,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17208</t>
+          <t>16179</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>38228</t>
+          <t>37344</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6134,12 +6134,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21715</t>
+          <t>22204</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>43018</t>
+          <t>44060</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>20,01%</t>
         </is>
       </c>
     </row>
@@ -6177,12 +6177,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3216</t>
+          <t>3478</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14281</t>
+          <t>15023</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6212,12 +6212,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>27955</t>
+          <t>27716</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>50058</t>
+          <t>50638</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6247,12 +6247,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>35040</t>
+          <t>34630</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>59908</t>
+          <t>58578</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>26,6%</t>
         </is>
       </c>
     </row>
@@ -6556,7 +6556,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7916</t>
+          <t>7145</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7773</t>
+          <t>8554</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7218</t>
+          <t>6366</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6668,12 +6668,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7495</t>
+          <t>7468</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>21985</t>
+          <t>22350</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>9166</t>
+          <t>8925</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>24381</t>
+          <t>24093</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -6746,12 +6746,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>23659</t>
+          <t>23900</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>43177</t>
+          <t>43723</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6781,12 +6781,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>20387</t>
+          <t>20512</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>42514</t>
+          <t>41476</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>49996</t>
+          <t>47261</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>79773</t>
+          <t>78376</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>27,62%</t>
         </is>
       </c>
     </row>
@@ -6859,12 +6859,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8874</t>
+          <t>8549</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>25277</t>
+          <t>24337</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>46249</t>
+          <t>45488</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>73395</t>
+          <t>72089</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>58046</t>
+          <t>56592</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>88452</t>
+          <t>89886</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,68%</t>
         </is>
       </c>
     </row>
@@ -6972,12 +6972,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>12593</t>
+          <t>13724</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>29885</t>
+          <t>29980</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7007,12 +7007,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>46863</t>
+          <t>48778</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>74566</t>
+          <t>74875</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7042,12 +7042,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>67265</t>
+          <t>65087</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>97332</t>
+          <t>96671</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,07%</t>
         </is>
       </c>
     </row>
@@ -7120,12 +7120,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2069</t>
+          <t>1976</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>12115</t>
+          <t>11896</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2062</t>
+          <t>2090</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>11962</t>
+          <t>11859</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -7198,12 +7198,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3089</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14249</t>
+          <t>14551</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7213,12 +7213,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7233,12 +7233,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>20218</t>
+          <t>19684</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>40510</t>
+          <t>41665</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7268,12 +7268,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>25556</t>
+          <t>26208</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>49965</t>
+          <t>49401</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7283,12 +7283,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,41%</t>
         </is>
       </c>
     </row>
@@ -7311,12 +7311,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4292</t>
+          <t>3809</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>16169</t>
+          <t>15906</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7326,12 +7326,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7346,12 +7346,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>29141</t>
+          <t>29788</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>53902</t>
+          <t>52982</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7361,12 +7361,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7381,12 +7381,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>37622</t>
+          <t>37746</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>61995</t>
+          <t>65453</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7396,12 +7396,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>23,07%</t>
         </is>
       </c>
     </row>
@@ -7655,7 +7655,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>5318</t>
+          <t>4452</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>8050</t>
+          <t>6772</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7705,7 +7705,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7720,12 +7720,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>979</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>9447</t>
+          <t>8813</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -8002,7 +8002,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7028</t>
+          <t>9204</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7456</t>
+          <t>7256</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19709</t>
+          <t>19438</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8441</t>
+          <t>8710</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22172</t>
+          <t>22710</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>36,46%</t>
         </is>
       </c>
     </row>
@@ -8110,12 +8110,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10197</t>
+          <t>9734</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19081</t>
+          <t>19060</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6792</t>
+          <t>6725</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18198</t>
+          <t>17323</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20134</t>
+          <t>19168</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35881</t>
+          <t>35095</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>56,35%</t>
         </is>
       </c>
     </row>
@@ -8223,12 +8223,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>987</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8020</t>
+          <t>8811</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8238,12 +8238,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5240</t>
+          <t>5658</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16856</t>
+          <t>17325</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7884</t>
+          <t>8235</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>22714</t>
+          <t>22121</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>35,52%</t>
         </is>
       </c>
     </row>
@@ -8336,12 +8336,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>879</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7069</t>
+          <t>7211</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9965</t>
+          <t>10613</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8386,12 +8386,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3978</t>
+          <t>3971</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15182</t>
+          <t>14436</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>23,18%</t>
         </is>
       </c>
     </row>
@@ -8489,7 +8489,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4991</t>
+          <t>5033</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5389</t>
+          <t>5891</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -8602,7 +8602,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4233</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8617,7 +8617,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5086</t>
+          <t>5154</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8652,7 +8652,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,28%</t>
         </is>
       </c>
     </row>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5056</t>
+          <t>4466</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8695,7 +8695,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8042</t>
+          <t>6616</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8730,7 +8730,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8750,7 +8750,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8483</t>
+          <t>9340</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8765,7 +8765,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>15,0%</t>
         </is>
       </c>
     </row>
@@ -9131,12 +9131,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>1487</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9219</t>
+          <t>9768</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9146,12 +9146,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9027</t>
+          <t>8964</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26658</t>
+          <t>27069</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9181,12 +9181,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11953</t>
+          <t>12318</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>30411</t>
+          <t>31901</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>17,57%</t>
         </is>
       </c>
     </row>
@@ -9244,12 +9244,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12522</t>
+          <t>12352</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>25765</t>
+          <t>26232</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9259,12 +9259,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>51,44%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5714</t>
+          <t>5749</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>22316</t>
+          <t>23637</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9294,12 +9294,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9314,12 +9314,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>21872</t>
+          <t>21904</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>41709</t>
+          <t>43508</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,96%</t>
         </is>
       </c>
     </row>
@@ -9357,12 +9357,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3973</t>
+          <t>3962</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13326</t>
+          <t>13065</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9372,12 +9372,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9392,12 +9392,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25831</t>
+          <t>24355</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47483</t>
+          <t>47686</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9407,12 +9407,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31026</t>
+          <t>32009</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>57023</t>
+          <t>56486</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,1%</t>
         </is>
       </c>
     </row>
@@ -9470,12 +9470,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>5063</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15009</t>
+          <t>15364</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9485,12 +9485,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9505,12 +9505,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27109</t>
+          <t>27453</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>50402</t>
+          <t>50173</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>35073</t>
+          <t>36132</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>60385</t>
+          <t>63377</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9555,12 +9555,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>34,9%</t>
         </is>
       </c>
     </row>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8547</t>
+          <t>8497</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>8215</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9673,7 +9673,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -9696,12 +9696,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5376</t>
+          <t>5068</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15916</t>
+          <t>15758</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9711,12 +9711,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16515</t>
+          <t>16102</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36517</t>
+          <t>37973</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9746,12 +9746,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9766,12 +9766,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>25372</t>
+          <t>24933</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>47097</t>
+          <t>49714</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9781,12 +9781,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>27,37%</t>
         </is>
       </c>
     </row>
@@ -9809,12 +9809,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>829</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7473</t>
+          <t>7685</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9824,12 +9824,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9844,12 +9844,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3934</t>
+          <t>4842</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>17735</t>
+          <t>18754</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9859,12 +9859,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9879,12 +9879,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7695</t>
+          <t>7477</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>23127</t>
+          <t>22455</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,36%</t>
         </is>
       </c>
     </row>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4416</t>
+          <t>4031</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9997,7 +9997,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3286</t>
+          <t>3814</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -10153,7 +10153,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6639</t>
+          <t>7011</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10168,7 +10168,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10188,7 +10188,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7510</t>
+          <t>7577</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10218,12 +10218,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1228</t>
+          <t>1256</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>11328</t>
+          <t>11710</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -10265,12 +10265,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>2310</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12832</t>
+          <t>12109</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10280,12 +10280,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10300,12 +10300,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>18642</t>
+          <t>18906</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>41348</t>
+          <t>41034</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10315,12 +10315,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>23786</t>
+          <t>23168</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>47572</t>
+          <t>47464</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10350,12 +10350,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,46%</t>
         </is>
       </c>
     </row>
@@ -10378,12 +10378,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>25572</t>
+          <t>26789</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>41326</t>
+          <t>43080</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10393,12 +10393,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>59,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10413,12 +10413,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14730</t>
+          <t>15306</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>35472</t>
+          <t>35917</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10428,12 +10428,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10448,12 +10448,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>44807</t>
+          <t>45064</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>72443</t>
+          <t>73099</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10463,12 +10463,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,97%</t>
         </is>
       </c>
     </row>
@@ -10491,12 +10491,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7062</t>
+          <t>6720</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>18504</t>
+          <t>18714</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10506,12 +10506,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10526,12 +10526,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>33564</t>
+          <t>33698</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>59659</t>
+          <t>59433</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10541,12 +10541,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10561,12 +10561,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>44872</t>
+          <t>45284</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>73135</t>
+          <t>73120</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,98%</t>
         </is>
       </c>
     </row>
@@ -10604,12 +10604,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>7036</t>
+          <t>7008</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>18674</t>
+          <t>19030</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10619,12 +10619,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -10639,12 +10639,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>31293</t>
+          <t>30624</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>56105</t>
+          <t>55836</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10654,12 +10654,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -10674,12 +10674,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>42987</t>
+          <t>42208</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>70377</t>
+          <t>71623</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10689,12 +10689,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>29,37%</t>
         </is>
       </c>
     </row>
@@ -10752,12 +10752,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>965</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8504</t>
+          <t>8435</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10767,12 +10767,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>977</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9233</t>
+          <t>9130</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10807,7 +10807,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -10830,12 +10830,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5085</t>
+          <t>5130</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>16395</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10845,12 +10845,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>16480</t>
+          <t>16272</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>39014</t>
+          <t>40246</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10880,12 +10880,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>25946</t>
+          <t>25617</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>51109</t>
+          <t>50892</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10915,12 +10915,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,87%</t>
         </is>
       </c>
     </row>
@@ -10943,12 +10943,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>9403</t>
+          <t>9401</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10958,7 +10958,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -10978,12 +10978,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5291</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>20263</t>
+          <t>20992</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10993,12 +10993,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11013,12 +11013,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>8984</t>
+          <t>8941</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>25963</t>
+          <t>25086</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -11061,7 +11061,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4023</t>
+          <t>3363</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11076,7 +11076,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11131,7 +11131,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4331</t>
+          <t>3784</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11146,7 +11146,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -11287,7 +11287,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>7022</t>
+          <t>8673</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11302,7 +11302,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11322,7 +11322,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>7776</t>
+          <t>8653</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11337,7 +11337,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11352,12 +11352,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>10521</t>
+          <t>10949</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11372,7 +11372,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -11624,32 +11624,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2205</t>
+          <t>2245</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>562</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5936</t>
+          <t>5234</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11659,32 +11659,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2744</t>
+          <t>3377</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5712</t>
+          <t>6687</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11694,32 +11694,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4948</t>
+          <t>5622</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8729</t>
+          <t>10398</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>11,5%</t>
         </is>
       </c>
     </row>
@@ -11737,32 +11737,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16708</t>
+          <t>17622</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12468</t>
+          <t>13395</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20540</t>
+          <t>22305</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>56,88%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11772,32 +11772,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18653</t>
+          <t>20592</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14031</t>
+          <t>15337</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23812</t>
+          <t>26317</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11807,32 +11807,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>35360</t>
+          <t>38213</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29278</t>
+          <t>30485</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41716</t>
+          <t>45443</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>50,24%</t>
         </is>
       </c>
     </row>
@@ -11850,32 +11850,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7132</t>
+          <t>7668</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3683</t>
+          <t>4283</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11184</t>
+          <t>12654</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11885,32 +11885,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11547</t>
+          <t>12994</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7756</t>
+          <t>8494</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16685</t>
+          <t>18647</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11920,32 +11920,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>18679</t>
+          <t>20661</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13052</t>
+          <t>14970</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>24899</t>
+          <t>27702</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,63%</t>
         </is>
       </c>
     </row>
@@ -11963,32 +11963,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11006</t>
+          <t>11526</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6532</t>
+          <t>7474</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14994</t>
+          <t>16310</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11998,32 +11998,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29169</t>
+          <t>32130</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23829</t>
+          <t>26601</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34400</t>
+          <t>37915</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>54,03%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12033,32 +12033,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>40175</t>
+          <t>43656</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33628</t>
+          <t>36602</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46681</t>
+          <t>51246</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>56,66%</t>
         </is>
       </c>
     </row>
@@ -12076,32 +12076,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2209</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>489</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5543</t>
+          <t>6650</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12111,22 +12111,22 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2363</t>
+          <t>2561</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>665</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5656</t>
+          <t>6544</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -12136,7 +12136,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12146,32 +12146,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4572</t>
+          <t>4895</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1801</t>
+          <t>2221</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8872</t>
+          <t>9621</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,64%</t>
         </is>
       </c>
     </row>
@@ -12189,32 +12189,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2228</t>
+          <t>2359</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>675</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5742</t>
+          <t>5810</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -12224,32 +12224,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5521</t>
+          <t>5876</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3099</t>
+          <t>3160</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9175</t>
+          <t>10282</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -12259,32 +12259,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>7749</t>
+          <t>8235</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4538</t>
+          <t>4609</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>12288</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,36%</t>
         </is>
       </c>
     </row>
@@ -12302,32 +12302,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>2699</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>995</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5551</t>
+          <t>5570</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12337,32 +12337,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7897</t>
+          <t>9257</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5537</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11955</t>
+          <t>14106</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12372,32 +12372,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>10541</t>
+          <t>11956</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6584</t>
+          <t>7664</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15562</t>
+          <t>17116</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,92%</t>
         </is>
       </c>
     </row>
@@ -12758,32 +12758,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3348</t>
+          <t>3701</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7039</t>
+          <t>8598</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12793,32 +12793,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>8839</t>
+          <t>9320</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5557</t>
+          <t>5661</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12978</t>
+          <t>14128</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12828,32 +12828,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>12186</t>
+          <t>13022</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8154</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17447</t>
+          <t>19680</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -12871,32 +12871,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20012</t>
+          <t>22122</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14340</t>
+          <t>16546</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>25875</t>
+          <t>29507</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -12906,32 +12906,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18262</t>
+          <t>20748</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13349</t>
+          <t>15166</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24003</t>
+          <t>28016</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -12941,32 +12941,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>38274</t>
+          <t>42870</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>31170</t>
+          <t>34152</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>47603</t>
+          <t>53385</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>18,19%</t>
         </is>
       </c>
     </row>
@@ -12984,32 +12984,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>6137</t>
+          <t>6593</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3299</t>
+          <t>3480</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10557</t>
+          <t>11356</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13019,32 +13019,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>42681</t>
+          <t>46363</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34565</t>
+          <t>37927</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51040</t>
+          <t>56515</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13054,32 +13054,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>48818</t>
+          <t>52955</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40787</t>
+          <t>42980</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>58477</t>
+          <t>63194</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,53%</t>
         </is>
       </c>
     </row>
@@ -13097,32 +13097,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>40146</t>
+          <t>42261</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>33211</t>
+          <t>35763</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>46846</t>
+          <t>49847</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>55,44%</t>
+          <t>54,46%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13132,32 +13132,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>111666</t>
+          <t>120540</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>102895</t>
+          <t>109442</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>121412</t>
+          <t>131256</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13167,32 +13167,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>151812</t>
+          <t>162801</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>140879</t>
+          <t>150045</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>163376</t>
+          <t>175922</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>59,93%</t>
         </is>
       </c>
     </row>
@@ -13210,32 +13210,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1807</t>
+          <t>1710</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>411</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5463</t>
+          <t>5336</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13245,32 +13245,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>7146</t>
+          <t>7679</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4024</t>
+          <t>4102</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12383</t>
+          <t>12619</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13280,32 +13280,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>8953</t>
+          <t>9389</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>5110</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>14344</t>
+          <t>14468</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -13323,32 +13323,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12970</t>
+          <t>13736</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8491</t>
+          <t>9167</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19161</t>
+          <t>20509</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13358,32 +13358,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>40391</t>
+          <t>44033</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>33009</t>
+          <t>35782</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>48764</t>
+          <t>53861</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13393,32 +13393,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>53361</t>
+          <t>57769</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>44358</t>
+          <t>46761</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>62560</t>
+          <t>68470</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,32%</t>
         </is>
       </c>
     </row>
@@ -13436,32 +13436,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>19528</t>
+          <t>20781</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13775</t>
+          <t>15173</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26632</t>
+          <t>28000</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13471,32 +13471,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>61078</t>
+          <t>66038</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>53090</t>
+          <t>56716</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>71185</t>
+          <t>76621</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13506,32 +13506,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>80606</t>
+          <t>86819</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>69861</t>
+          <t>74186</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>92198</t>
+          <t>98489</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>33,55%</t>
         </is>
       </c>
     </row>
@@ -13549,7 +13549,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -13559,12 +13559,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3301</t>
+          <t>3404</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -13574,7 +13574,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -13584,32 +13584,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1584</t>
+          <t>1787</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>435</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4718</t>
+          <t>4881</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13619,32 +13619,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>2519</t>
+          <t>2820</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>6245</t>
+          <t>6450</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -13775,7 +13775,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>647</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -13785,12 +13785,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2941</t>
+          <t>3757</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -13800,7 +13800,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13810,32 +13810,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2460</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>761</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5712</t>
+          <t>6091</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13845,17 +13845,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2857</t>
+          <t>3108</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>7852</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13870,7 +13870,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -13892,32 +13892,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>5552</t>
+          <t>5947</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2775</t>
+          <t>2947</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9954</t>
+          <t>10199</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13927,17 +13927,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>11582</t>
+          <t>12697</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7607</t>
+          <t>8592</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17087</t>
+          <t>19055</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13947,12 +13947,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13962,22 +13962,22 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>17135</t>
+          <t>18644</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>12036</t>
+          <t>13099</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>23709</t>
+          <t>25813</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
@@ -13987,7 +13987,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -14005,32 +14005,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>36720</t>
+          <t>39743</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>29755</t>
+          <t>31882</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>44707</t>
+          <t>48288</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14040,32 +14040,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>36915</t>
+          <t>41340</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>29544</t>
+          <t>32831</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>46061</t>
+          <t>50323</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14075,32 +14075,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>73635</t>
+          <t>81083</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>61941</t>
+          <t>69153</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>85141</t>
+          <t>93755</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,42%</t>
         </is>
       </c>
     </row>
@@ -14118,32 +14118,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>13269</t>
+          <t>14260</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8866</t>
+          <t>9375</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20107</t>
+          <t>21685</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14153,32 +14153,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>54228</t>
+          <t>59356</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>45255</t>
+          <t>49485</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>64689</t>
+          <t>70898</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14188,32 +14188,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>67497</t>
+          <t>73617</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>57999</t>
+          <t>61989</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>78421</t>
+          <t>85717</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,32%</t>
         </is>
       </c>
     </row>
@@ -14231,32 +14231,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>51152</t>
+          <t>53787</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>43587</t>
+          <t>45758</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>58844</t>
+          <t>62271</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>49,54%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -14266,32 +14266,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>140834</t>
+          <t>152671</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>129858</t>
+          <t>139710</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>152218</t>
+          <t>165284</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>60,01%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -14301,32 +14301,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>191987</t>
+          <t>206457</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>178211</t>
+          <t>191274</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>204443</t>
+          <t>222974</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>58,07%</t>
         </is>
       </c>
     </row>
@@ -14344,32 +14344,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>4016</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1506</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8489</t>
+          <t>8681</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14379,32 +14379,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>9509</t>
+          <t>10239</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5800</t>
+          <t>6525</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>14629</t>
+          <t>16865</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14414,32 +14414,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>13524</t>
+          <t>14284</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>9491</t>
+          <t>9414</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>20514</t>
+          <t>21425</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -14457,32 +14457,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>15198</t>
+          <t>16095</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10552</t>
+          <t>10915</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>22156</t>
+          <t>22962</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14492,32 +14492,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>45911</t>
+          <t>49909</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>37689</t>
+          <t>41110</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>56308</t>
+          <t>59639</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14527,32 +14527,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>61110</t>
+          <t>66003</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>50999</t>
+          <t>55311</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>71897</t>
+          <t>78774</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,51%</t>
         </is>
       </c>
     </row>
@@ -14570,32 +14570,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>22173</t>
+          <t>23480</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>15949</t>
+          <t>16799</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>29888</t>
+          <t>31442</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14605,32 +14605,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>68974</t>
+          <t>75295</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>59452</t>
+          <t>66317</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>79282</t>
+          <t>86929</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14640,32 +14640,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>91148</t>
+          <t>98775</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>79688</t>
+          <t>86824</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>104508</t>
+          <t>112260</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,23%</t>
         </is>
       </c>
     </row>
@@ -14683,7 +14683,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -14693,12 +14693,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3112</t>
+          <t>4133</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -14708,7 +14708,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14718,22 +14718,22 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1584</t>
+          <t>1787</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>464</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4431</t>
+          <t>4930</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -14743,7 +14743,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14753,32 +14753,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>2519</t>
+          <t>2820</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>809</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>5700</t>
+          <t>6235</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -14909,7 +14909,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>647</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -14919,12 +14919,12 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3839</t>
+          <t>3478</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -14934,7 +14934,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -14944,32 +14944,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2460</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>819</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>5844</t>
+          <t>6137</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -14979,17 +14979,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>2857</t>
+          <t>3108</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>6110</t>
+          <t>7377</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -14999,12 +14999,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
